--- a/public/paper-template.xlsx
+++ b/public/paper-template.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="69">
   <si>
     <t>{{발행처로고}}</t>
   </si>
@@ -166,6 +166,12 @@
   </si>
   <si>
     <t>쪽 번호. 값으로 줄 수 없어 시스템이 채웁니다.</t>
+  </si>
+  <si>
+    <t>{{묶음:품목.분류}}</t>
+  </si>
+  <si>
+    <t>반복 여러 줄에 «세로로 걸치는» 칸. 값이 같은 줄끼리 저절로 묶여 한 칸이 됩니다(경첩 4줄 옆의 「경첩」). 「반복」 줄에 한 번만 적습니다.</t>
   </si>
   <si>
     <t>행의 역할 (Z열)</t>
@@ -739,7 +745,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -769,8 +775,8 @@
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
     </row>
-    <row r="3" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="18" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
@@ -798,43 +804,43 @@
       <c r="W4" s="6"/>
       <c r="X4" s="6"/>
     </row>
-    <row r="5" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="7" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="9" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="10" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="11" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="12" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="13" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="14" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="16" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="42" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>8</v>
@@ -890,13 +896,13 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1100,74 +1106,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="3:4" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="3:4" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="C10:C80">
@@ -1184,13 +1122,13 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1301,28 +1239,28 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="12" t="s">
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
         <v>52</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1359,26 +1297,26 @@
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="12" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1386,7 +1324,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1394,7 +1332,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1402,19 +1340,27 @@
         <v>20</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>66</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/public/paper-template.xlsx
+++ b/public/paper-template.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="74">
   <si>
     <t>{{발행처로고}}</t>
   </si>
@@ -162,18 +162,18 @@
     <t>집계. 합계 · 개수 · 평균 셋만 됩니다. 쉼표로 여러 열을 더할 수 있습니다.</t>
   </si>
   <si>
+    <t>{{들여:품목.품명}}</t>
+  </si>
+  <si>
+    <t>트리 줄. 그 줄의 «깊이»만큼 글자가 밀립니다. 보통 품명 칸 하나에만 붙입니다 — 수량·단가는 제 열에 그대로 서야 세로로 읽힙니다.</t>
+  </si>
+  <si>
     <t>{{@쪽}} {{@총쪽}}</t>
   </si>
   <si>
     <t>쪽 번호. 값으로 줄 수 없어 시스템이 채웁니다.</t>
   </si>
   <si>
-    <t>{{묶음:품목.분류}}</t>
-  </si>
-  <si>
-    <t>반복 여러 줄에 «세로로 걸치는» 칸. 값이 같은 줄끼리 저절로 묶여 한 칸이 됩니다(경첩 4줄 옆의 「경첩」). 「반복」 줄에 한 번만 적습니다.</t>
-  </si>
-  <si>
     <t>행의 역할 (Z열)</t>
   </si>
   <si>
@@ -195,6 +195,9 @@
     <t>묶음이 바뀔 때 / 끝날 때 한 번. 소계 자리입니다.</t>
   </si>
   <si>
+    <t>트리에서는 「그룹머리」 없이 「그룹꼬리」만 적어도 됩니다 — 깊이 1인 줄이 다시 나오는 것이 곧 앞 묶음의 끝이라, 묶음 기준을 구조가 이미 말하고 있습니다.</t>
+  </si>
+  <si>
     <t>반복</t>
   </si>
   <si>
@@ -205,6 +208,18 @@
   </si>
   <si>
     <t>마지막 쪽에만 나옵니다.</t>
+  </si>
+  <si>
+    <t>줄마다 깊이가 다른 표</t>
+  </si>
+  <si>
+    <t>내역서처럼 「주방 › 상부장 › 옵션1」이 딸리는 표는, 깊이를 담을 열을 하나 만들고 「필드」 시트에서 그 열의 종류를 «깊이»로 둡니다(1이 가장 얕습니다).</t>
+  </si>
+  <si>
+    <t>그 열은 종이에 안 찍힙니다 — 들여쓰기와 소계 경계가 읽어 가는 축입니다. 서식에는 «반복» 줄이 하나만 있고, 몇 줄이 될지는 값이 정합니다.</t>
+  </si>
+  <si>
+    <t>중간 줄도 자기 금액을 갖습니다(상부장은 옵션의 합이 아닙니다). 소계는 그 묶음에 딸린 모든 줄을 더하므로, 부모를 자식의 합으로 넣으면 두 번 더해집니다.</t>
   </si>
   <si>
     <t>표준 머리에 있는 것</t>
@@ -745,7 +760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -775,8 +790,8 @@
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
     </row>
-    <row r="3" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="18" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
@@ -804,43 +819,43 @@
       <c r="W4" s="6"/>
       <c r="X4" s="6"/>
     </row>
-    <row r="5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="7" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="9" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="12" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="13" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="14" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="16" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
     <row r="42" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>8</v>
@@ -896,13 +911,13 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1106,13 +1121,81 @@
         <v>20</v>
       </c>
     </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="3:4" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="C10:C80">
-      <formula1>"글자,숫자,금액,날짜,여러 줄,선택,예아니오,이미지"</formula1>
+      <formula1>"글자,숫자,금액,날짜,여러 줄,선택,예아니오,이미지,깊이"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C2:C80">
-      <formula1>"글자,숫자,금액,날짜,여러 줄,선택,예아니오,이미지"</formula1>
+      <formula1>"글자,숫자,금액,날짜,여러 줄,선택,예아니오,이미지,깊이"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D10:D80">
       <formula1>"필수"</formula1>
@@ -1122,13 +1205,13 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1239,7 +1322,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>50</v>
       </c>
@@ -1289,42 +1372,42 @@
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>59</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>61</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="12" t="s">
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
         <v>64</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1348,19 +1431,67 @@
         <v>20</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="B28" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
         <v>68</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/public/paper-template.xlsx
+++ b/public/paper-template.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="78">
   <si>
     <t>{{발행처로고}}</t>
   </si>
@@ -168,6 +168,12 @@
     <t>트리 줄. 그 줄의 «깊이»만큼 글자가 밀립니다. 보통 품명 칸 하나에만 붙입니다 — 수량·단가는 제 열에 그대로 서야 세로로 읽힙니다.</t>
   </si>
   <si>
+    <t>{{번호:품목.품명}}</t>
+  </si>
+  <si>
+    <t>구획 제목의 번호 — 「1. 주방」 「2. 후드」. 묶음을 여는 줄에만 붙고, 번호는 데이터가 아니라 그 표에서의 «자리»에서 나옵니다.</t>
+  </si>
+  <si>
     <t>{{@쪽}} {{@총쪽}}</t>
   </si>
   <si>
@@ -198,6 +204,9 @@
     <t>트리에서는 「그룹머리」 없이 「그룹꼬리」만 적어도 됩니다 — 깊이 1인 줄이 다시 나오는 것이 곧 앞 묶음의 끝이라, 묶음 기준을 구조가 이미 말하고 있습니다.</t>
   </si>
   <si>
+    <t>「열머리」를 「그룹머리」 «아래»에 두면 구획마다 열머리가 다시 납니다. «위»에 두면 표 전체에 한 번입니다 — 적힌 순서가 곧 발화 순서입니다.</t>
+  </si>
+  <si>
     <t>반복</t>
   </si>
   <si>
@@ -219,7 +228,10 @@
     <t>그 열은 종이에 안 찍힙니다 — 들여쓰기와 소계 경계가 읽어 가는 축입니다. 서식에는 «반복» 줄이 하나만 있고, 몇 줄이 될지는 값이 정합니다.</t>
   </si>
   <si>
-    <t>중간 줄도 자기 금액을 갖습니다(상부장은 옵션의 합이 아닙니다). 소계는 그 묶음에 딸린 모든 줄을 더하므로, 부모를 자식의 합으로 넣으면 두 번 더해집니다.</t>
+    <t>깊이 1을 «구획 제목»으로 쓰면(「그룹머리」로 두면) 그 줄은 반복에서 빠집니다 — 제목이 가져가므로 같은 이름이 두 번 나오지 않습니다. 이때 제목 줄은 자기 금액을 갖지 않고, 그 구획의 수는 소계가 말합니다.</t>
+  </si>
+  <si>
+    <t>들여쓰기는 «그려지는 줄 중 가장 얕은 깊이»가 기준입니다. 제목이 깊이 1을 가져가면 깊이 2가 기준선이 되어 표가 통째로 밀려 들어가지 않습니다.</t>
   </si>
   <si>
     <t>표준 머리에 있는 것</t>
@@ -1211,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1332,26 +1344,26 @@
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="12" t="s">
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
         <v>54</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1372,15 +1384,15 @@
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>61</v>
@@ -1388,26 +1400,26 @@
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>62</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="11" t="s">
-        <v>20</v>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1415,15 +1427,15 @@
         <v>20</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>66</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1431,7 +1443,7 @@
         <v>20</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1439,15 +1451,15 @@
         <v>20</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>20</v>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1455,7 +1467,7 @@
         <v>20</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1463,15 +1475,15 @@
         <v>20</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>71</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1479,15 +1491,39 @@
         <v>20</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/public/paper-template.xlsx
+++ b/public/paper-template.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="80">
   <si>
     <t>{{발행처로고}}</t>
   </si>
@@ -142,6 +142,12 @@
   </si>
   <si>
     <t>기본 18pt(=한 칸). 높은 칸은 36pt·54pt처럼 18의 배수로 둡니다.</t>
+  </si>
+  <si>
+    <t>세로 정렬</t>
+  </si>
+  <si>
+    <t>엑셀은 세로 정렬을 안 정하면 «아래»에 붙여 그리지만, 인쇄물은 «가운데»로 나갑니다. 엑셀 화면과 결과를 맞추려면 세로 정렬을 «가운데»로 지정해 두세요(결과가 바뀌지는 않습니다).</t>
   </si>
   <si>
     <t>값이 들어갈 자리</t>
@@ -1223,7 +1229,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1288,31 +1294,31 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="12" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>45</v>
@@ -1352,26 +1358,26 @@
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="12" t="s">
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
         <v>56</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1392,10 +1398,10 @@
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1403,12 +1409,12 @@
         <v>20</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>64</v>
@@ -1424,26 +1430,26 @@
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" s="12" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1451,7 +1457,7 @@
         <v>20</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1459,7 +1465,7 @@
         <v>20</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1467,7 +1473,7 @@
         <v>20</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1475,23 +1481,23 @@
         <v>20</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B33" s="12" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1499,7 +1505,7 @@
         <v>20</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1507,7 +1513,7 @@
         <v>20</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -1515,15 +1521,23 @@
         <v>20</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>77</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/public/paper-template.xlsx
+++ b/public/paper-template.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="79">
   <si>
     <t>{{발행처로고}}</t>
   </si>
@@ -24,133 +24,130 @@
     <t>문 서 제 목</t>
   </si>
   <si>
+    <t>▼ 이 행의 역할</t>
+  </si>
+  <si>
+    <t>▽ 여기부터 본문입니다. 칸을 병합하고 테두리를 그려 만드세요. 높은 칸은 «세로 병합»으로. (이 줄은 지우세요)</t>
+  </si>
+  <si>
+    <t>{{발행처명}}　{{발행처주소}}　{{발행처전화}}</t>
+  </si>
+  <si>
+    <t>{{@쪽}} / {{@총쪽}}</t>
+  </si>
+  <si>
+    <t>꼬리말</t>
+  </si>
+  <si>
+    <t>이름</t>
+  </si>
+  <si>
+    <t>라벨</t>
+  </si>
+  <si>
+    <t>종류</t>
+  </si>
+  <si>
+    <t>필수</t>
+  </si>
+  <si>
+    <t>배열</t>
+  </si>
+  <si>
+    <t>── 표준(모든 문서 공통) ──</t>
+  </si>
+  <si>
+    <t>발행처로고</t>
+  </si>
+  <si>
+    <t>발행처 로고</t>
+  </si>
+  <si>
+    <t>이미지</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>발행처명</t>
+  </si>
+  <si>
+    <t>발행처 이름</t>
+  </si>
+  <si>
+    <t>글자</t>
+  </si>
+  <si>
+    <t>발행처사업자번호</t>
+  </si>
+  <si>
+    <t>발행처 사업자번호</t>
+  </si>
+  <si>
+    <t>발행처주소</t>
+  </si>
+  <si>
+    <t>발행처 주소</t>
+  </si>
+  <si>
+    <t>발행처전화</t>
+  </si>
+  <si>
+    <t>발행처 전화</t>
+  </si>
+  <si>
     <t>문서번호</t>
   </si>
   <si>
+    <t>작성일자</t>
+  </si>
+  <si>
+    <t>날짜</t>
+  </si>
+  <si>
+    <t>담당자</t>
+  </si>
+  <si>
+    <t>검토자</t>
+  </si>
+  <si>
+    <t>승인자</t>
+  </si>
+  <si>
+    <t>시작하는 법</t>
+  </si>
+  <si>
+    <t>「양식」 시트의 24열 × 42행이 A4 한 쪽입니다. 표준 머리(1~7행)와 꼬리(42행)는 이미 놓여 있으니 8행부터 채우면 됩니다.</t>
+  </si>
+  <si>
+    <t>칸을 병합하고 테두리를 그려서 문서를 만듭니다. 회색 글씨는 값이 들어갈 자리 표시입니다.</t>
+  </si>
+  <si>
+    <t>건드리지 말 것</t>
+  </si>
+  <si>
+    <t>열 너비</t>
+  </si>
+  <si>
+    <t>넓은 칸이 필요하면 옆 칸과 «병합»합니다. 열 너비를 바꾸면 24열 격자가 깨집니다.</t>
+  </si>
+  <si>
+    <t>행 높이</t>
+  </si>
+  <si>
+    <t>기본 18pt(=한 칸). 높은 칸은 36pt·54pt처럼 18의 배수로 둡니다.</t>
+  </si>
+  <si>
+    <t>세로 정렬</t>
+  </si>
+  <si>
+    <t>엑셀은 세로 정렬을 안 정하면 «아래»에 붙여 그리지만, 인쇄물은 «가운데»로 나갑니다. 엑셀 화면과 결과를 맞추려면 세로 정렬을 «가운데»로 지정해 두세요(결과가 바뀌지는 않습니다).</t>
+  </si>
+  <si>
+    <t>값이 들어갈 자리</t>
+  </si>
+  <si>
     <t>{{문서번호}}</t>
-  </si>
-  <si>
-    <t>▼ 이 행의 역할</t>
-  </si>
-  <si>
-    <t>작성일자</t>
-  </si>
-  <si>
-    <t>{{작성일자}}</t>
-  </si>
-  <si>
-    <t>▽ 여기부터 본문입니다. 칸을 병합하고 테두리를 그려 만드세요. 높은 칸은 «세로 병합»으로. (이 줄은 지우세요)</t>
-  </si>
-  <si>
-    <t>{{발행처명}}　{{발행처주소}}　{{발행처전화}}</t>
-  </si>
-  <si>
-    <t>{{@쪽}} / {{@총쪽}}</t>
-  </si>
-  <si>
-    <t>꼬리말</t>
-  </si>
-  <si>
-    <t>이름</t>
-  </si>
-  <si>
-    <t>라벨</t>
-  </si>
-  <si>
-    <t>종류</t>
-  </si>
-  <si>
-    <t>필수</t>
-  </si>
-  <si>
-    <t>배열</t>
-  </si>
-  <si>
-    <t>── 표준(모든 문서 공통) ──</t>
-  </si>
-  <si>
-    <t>발행처로고</t>
-  </si>
-  <si>
-    <t>발행처 로고</t>
-  </si>
-  <si>
-    <t>이미지</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>발행처명</t>
-  </si>
-  <si>
-    <t>발행처 이름</t>
-  </si>
-  <si>
-    <t>글자</t>
-  </si>
-  <si>
-    <t>발행처사업자번호</t>
-  </si>
-  <si>
-    <t>발행처 사업자번호</t>
-  </si>
-  <si>
-    <t>발행처주소</t>
-  </si>
-  <si>
-    <t>발행처 주소</t>
-  </si>
-  <si>
-    <t>발행처전화</t>
-  </si>
-  <si>
-    <t>발행처 전화</t>
-  </si>
-  <si>
-    <t>날짜</t>
-  </si>
-  <si>
-    <t>담당자</t>
-  </si>
-  <si>
-    <t>검토자</t>
-  </si>
-  <si>
-    <t>승인자</t>
-  </si>
-  <si>
-    <t>시작하는 법</t>
-  </si>
-  <si>
-    <t>「양식」 시트의 24열 × 42행이 A4 한 쪽입니다. 표준 머리(1~7행)와 꼬리(42행)는 이미 놓여 있으니 8행부터 채우면 됩니다.</t>
-  </si>
-  <si>
-    <t>칸을 병합하고 테두리를 그려서 문서를 만듭니다. 회색 글씨는 값이 들어갈 자리 표시입니다.</t>
-  </si>
-  <si>
-    <t>건드리지 말 것</t>
-  </si>
-  <si>
-    <t>열 너비</t>
-  </si>
-  <si>
-    <t>넓은 칸이 필요하면 옆 칸과 «병합»합니다. 열 너비를 바꾸면 24열 격자가 깨집니다.</t>
-  </si>
-  <si>
-    <t>행 높이</t>
-  </si>
-  <si>
-    <t>기본 18pt(=한 칸). 높은 칸은 36pt·54pt처럼 18의 배수로 둡니다.</t>
-  </si>
-  <si>
-    <t>세로 정렬</t>
-  </si>
-  <si>
-    <t>엑셀은 세로 정렬을 안 정하면 «아래»에 붙여 그리지만, 인쇄물은 «가운데»로 나갑니다. 엑셀 화면과 결과를 맞추려면 세로 정렬을 «가운데»로 지정해 두세요(결과가 바뀌지는 않습니다).</t>
-  </si>
-  <si>
-    <t>값이 들어갈 자리</t>
   </si>
   <si>
     <t>「필드」 시트에 적은 이름을 두 겹 중괄호로 씁니다.</t>
@@ -262,7 +259,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -279,11 +276,6 @@
       <b/>
       <color rgb="FF16181C"/>
       <sz val="18"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <color rgb="FF16181C"/>
-      <sz val="8"/>
       <name val="맑은 고딕"/>
     </font>
     <font>
@@ -327,27 +319,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF6E7480"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF6E7480"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF6E7480"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF6E7480"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -363,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -371,28 +348,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -763,19 +734,12 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="Z1" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Z1" s="5" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -796,46 +760,39 @@
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-      <c r="R2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
     <row r="4" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
     </row>
     <row r="5" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
     <row r="6" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
@@ -875,46 +832,42 @@
     <row r="40" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
     <row r="41" ht="18" customHeight="1" spans="26:26" x14ac:dyDescent="0.25"/>
     <row r="42" ht="18" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-      <c r="N42" s="7"/>
-      <c r="O42" s="7"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="7"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="T42" s="8"/>
-      <c r="U42" s="8"/>
-      <c r="V42" s="8"/>
-      <c r="W42" s="8"/>
-      <c r="X42" s="8"/>
-      <c r="Z42" s="9" t="s">
-        <v>10</v>
+      <c r="A42" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="5"/>
+      <c r="R42" s="5"/>
+      <c r="S42" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T42" s="6"/>
+      <c r="U42" s="6"/>
+      <c r="V42" s="6"/>
+      <c r="W42" s="6"/>
+      <c r="X42" s="6"/>
+      <c r="Z42" s="7" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="5">
     <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:Q2"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="U1:X1"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:X2"/>
+    <mergeCell ref="D1:U2"/>
     <mergeCell ref="A4:X4"/>
     <mergeCell ref="A42:R42"/>
     <mergeCell ref="S42:X42"/>
@@ -945,198 +898,198 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="10" t="s">
+    </row>
+    <row r="2" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25"/>
@@ -1236,308 +1189,308 @@
     <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" ht="26" customHeight="1" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="12" t="s">
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="12" t="s">
+      <c r="B5" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B7" s="10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+    <row r="8" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+    <row r="9" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B10" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="12" t="s">
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="B12" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="12" t="s">
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="B13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="12" t="s">
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="B14" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="12" t="s">
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="B15" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="12" t="s">
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="B16" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="12" t="s">
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="B18" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="B19" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="12" t="s">
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="B20" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="12" t="s">
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="B21" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="12" t="s">
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="12" t="s">
+    <row r="23" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="12" t="s">
+    <row r="24" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="B24" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B24" s="12" t="s">
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
+      <c r="B25" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="12" t="s">
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="B27" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" s="12" t="s">
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B29" s="12" t="s">
+    <row r="30" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B30" s="12" t="s">
+    <row r="31" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B31" s="12" t="s">
+    <row r="32" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="32" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" ht="26" customHeight="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
+      <c r="B33" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B34" s="12" t="s">
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B35" s="12" t="s">
+    <row r="36" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" s="10" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B36" s="12" t="s">
+    <row r="37" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="37" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
+      <c r="B38" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
